--- a/01-Spec/01-WallE-ESP32S3-WROOM-1-N16R8-GPIO信息_V1.0.xlsx
+++ b/01-Spec/01-WallE-ESP32S3-WROOM-1-N16R8-GPIO信息_V1.0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OK\Desktop\毕设-瓦力\01-Spec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OK\Desktop\WallE_Graduation\01-Spec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1894FCF5-3EBA-413F-B30F-886017588F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3420A8BD-564B-4478-BE22-B8FF6A4688EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -994,7 +994,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1013,6 +1013,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1026,7 +1032,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1037,6 +1043,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1050,8 +1059,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1353,10 +1362,10 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="9"/>
+      <c r="E1" s="5"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -1377,8 +1386,8 @@
       <c r="C2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -1397,8 +1406,8 @@
         <v>52</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -1417,8 +1426,8 @@
         <v>53</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -1439,8 +1448,8 @@
       <c r="C5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -1452,15 +1461,15 @@
       <c r="N5" s="3"/>
     </row>
     <row r="6" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="10" t="s">
         <v>54</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -1472,15 +1481,15 @@
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="10" t="s">
         <v>55</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -1492,10 +1501,10 @@
       <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="10" t="s">
         <v>56</v>
       </c>
       <c r="C8" s="2"/>
@@ -1512,10 +1521,10 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="10" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="2"/>
@@ -1532,10 +1541,10 @@
       <c r="N9" s="3"/>
     </row>
     <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="10" t="s">
         <v>58</v>
       </c>
       <c r="C10" s="2"/>
@@ -1552,10 +1561,10 @@
       <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="10" t="s">
         <v>67</v>
       </c>
       <c r="C11" s="2"/>
@@ -1572,10 +1581,10 @@
       <c r="N11" s="3"/>
     </row>
     <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="10" t="s">
         <v>68</v>
       </c>
       <c r="C12" s="2"/>
@@ -1592,10 +1601,10 @@
       <c r="N12" s="3"/>
     </row>
     <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="10" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="2"/>
@@ -1612,10 +1621,10 @@
       <c r="N13" s="3"/>
     </row>
     <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C14" s="2"/>
@@ -1632,10 +1641,10 @@
       <c r="N14" s="3"/>
     </row>
     <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="10" t="s">
         <v>71</v>
       </c>
       <c r="C15" s="2"/>
@@ -1672,10 +1681,10 @@
       <c r="N16" s="3"/>
     </row>
     <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="2"/>
@@ -1692,10 +1701,10 @@
       <c r="N17" s="3"/>
     </row>
     <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="10" t="s">
         <v>60</v>
       </c>
       <c r="C18" s="2"/>
@@ -1712,10 +1721,10 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C19" s="2"/>
@@ -1732,10 +1741,10 @@
       <c r="N19" s="3"/>
     </row>
     <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="10" t="s">
         <v>62</v>
       </c>
       <c r="C20" s="2"/>
@@ -1815,7 +1824,7 @@
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="8" t="s">
         <v>87</v>
       </c>
       <c r="C24" s="2"/>
@@ -1835,7 +1844,7 @@
       <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="7"/>
+      <c r="B25" s="8"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -1853,7 +1862,7 @@
       <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="7"/>
+      <c r="B26" s="8"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -1871,7 +1880,7 @@
       <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="7"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -1889,7 +1898,7 @@
       <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C28" s="2"/>
@@ -1909,7 +1918,7 @@
       <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="8"/>
+      <c r="B29" s="9"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
@@ -1927,7 +1936,7 @@
       <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="8"/>
+      <c r="B30" s="9"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -1945,7 +1954,7 @@
       <c r="A31" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="8"/>
+      <c r="B31" s="9"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -1963,7 +1972,7 @@
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="8"/>
+      <c r="B32" s="9"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -1981,7 +1990,7 @@
       <c r="A33" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="8"/>
+      <c r="B33" s="9"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -1999,7 +2008,7 @@
       <c r="A34" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="8"/>
+      <c r="B34" s="9"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
@@ -2017,7 +2026,7 @@
       <c r="A35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="8"/>
+      <c r="B35" s="9"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -2035,7 +2044,7 @@
       <c r="A36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="8"/>
+      <c r="B36" s="9"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -2053,7 +2062,7 @@
       <c r="A37" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="8"/>
+      <c r="B37" s="9"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -2071,7 +2080,7 @@
       <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="8"/>
+      <c r="B38" s="9"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -2089,7 +2098,7 @@
       <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="8"/>
+      <c r="B39" s="9"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -2344,11 +2353,11 @@
       <c r="N51" s="3"/>
     </row>
     <row r="52" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -2362,9 +2371,9 @@
       <c r="N52" s="3"/>
     </row>
     <row r="53" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
@@ -2378,9 +2387,9 @@
       <c r="N53" s="3"/>
     </row>
     <row r="54" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -2394,9 +2403,9 @@
       <c r="N54" s="3"/>
     </row>
     <row r="55" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
